--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260907.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260907.xlsx
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>30,691</t>
+          <t>146,245</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>146,245</t>
+          <t>30,691</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
